--- a/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
+++ b/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2446,131 +2446,148 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>book_settings</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>최종 수정 일시</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>split_pages</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>한 장에 든 두 쪽을 좌·우로 나눠 보기. 펼쳐 스캔한 책은 그대로 보면 글자가 절반 크기가 된다</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>[anchors] 앵커 (주석·캡처 공유)</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>split_right_to_left</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>분할 시 오른쪽 반쪽을 먼저 읽는가 (세로쓰기 등)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>split_prompted</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>내부 순번</t>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>좌우 분할을 권해 봤는가. 거절한 사람에게 매번 묻지 않기 위함</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>동기화 기준 전역 고유 ID</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>crop_prompted</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>자동 여백 크롭을 권해 봤는가. 거절한 사람에게 매번 묻지 않기 위함</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>anchors</t>
+          <t>book_settings</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2579,49 +2596,25 @@
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>최종 수정 일시</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>'text'</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>[anchors] 앵커 (주석·캡처 공유)</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2631,7 +2624,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2644,15 +2637,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>페이지 번호 (1부터)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2661,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>rects</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2678,10 +2675,14 @@
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -2693,24 +2694,28 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>quote_text</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2727,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>prefix_text</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2732,14 +2737,18 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>'text'</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
+          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
         </is>
       </c>
     </row>
@@ -2751,24 +2760,28 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>suffix_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>뒤 문맥 40자</t>
+          <t>페이지 번호 (1부터)</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2793,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>document_checksum</t>
+          <t>rects</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2797,7 +2810,7 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
+          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2822,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>video_time_ms</t>
+          <t>quote_text</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2826,7 +2839,7 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
+          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
         </is>
       </c>
     </row>
@@ -2838,28 +2851,24 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>is_orphan</t>
+          <t>prefix_text</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
+          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2880,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>suffix_text</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2881,39 +2890,55 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>뒤 문맥 40자</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>[annotations] 주석</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr"/>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>anchors</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>document_checksum</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>video_time_ms</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2923,39 +2948,31 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>is_orphan</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2963,32 +2980,32 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
+          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2997,49 +3014,25 @@
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
+      <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>annotations</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>anchor_id</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>anchors.id</t>
-        </is>
-      </c>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>[annotations] 주석</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr"/>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3049,12 +3042,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>anno_type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3062,11 +3055,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>주석 유형 (highlight / underline / strikeout / note)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3078,12 +3079,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>color_slot</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3091,15 +3092,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
+          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
         </is>
       </c>
     </row>
@@ -3111,24 +3112,28 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>사용자 메모</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3145,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3154,10 +3159,14 @@
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>anchors.id</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3178,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>anno_type</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3186,7 +3195,7 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>최종 수정 일시</t>
+          <t>주석 유형 (highlight / underline / strikeout / note)</t>
         </is>
       </c>
     </row>
@@ -3198,54 +3207,74 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>color_slot</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>소프트 삭제</t>
+          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>[captures] 캡처 기록</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="5" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>annotations</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>사용자 메모</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3253,31 +3282,23 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3291,82 +3312,54 @@
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>동기화 기준 전역 고유 ID</t>
+          <t>최종 수정 일시</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
+      <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>소프트 삭제</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>captures</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>anchor_id</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
-        </is>
-      </c>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>[captures] 캡처 기록</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr"/>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3376,24 +3369,32 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>image_path</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>저장된 이미지 경로</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3406,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3418,15 +3419,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>캡처 해상도 (150/300/600)</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3438,24 +3439,28 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ocr_text</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>영역 OCR 결과 (서버 처리)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3467,24 +3472,28 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3505,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>image_path</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3506,76 +3515,88 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>저장된 이미지 경로</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>[annotation_events] 주석 이벤트 (append-only)</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr"/>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>captures</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>캡처 해상도 (150/300/600)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ocr_text</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>영역 OCR 결과 (서버 처리)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3585,30 +3606,26 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>이벤트 고유 ID</t>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>target_type</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3625,42 +3642,22 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>대상 종류 (annotation / bookmark / capture)</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>annotation_events</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>target_uuid</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>대상 레코드 UUID</t>
-        </is>
-      </c>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>[annotation_events] 주석 이벤트 (append-only)</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr"/>
+      <c r="C85" s="4" t="inlineStr"/>
+      <c r="D85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3670,12 +3667,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>op</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3683,11 +3680,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>연산 (create / update / delete)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3704,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3709,14 +3714,18 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>변경 내용 JSON</t>
+          <t>이벤트 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3737,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>device_id</t>
+          <t>target_type</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3745,7 +3754,7 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>작성 기기 식별자</t>
+          <t>대상 종류 (annotation / bookmark / capture)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3766,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>target_uuid</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3778,7 +3787,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
+          <t>대상 레코드 UUID</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3799,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>synced_at</t>
+          <t>op</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3800,44 +3809,60 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>서버 반영 일시. NULL 이면 미전송</t>
+          <t>연산 (create / update / delete)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>[page_texts] 페이지 텍스트 캐시</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr"/>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>annotation_events</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>변경 내용 JSON</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>device_id</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3845,36 +3870,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>page_fts 의 content_rowid</t>
+          <t>작성 기기 식별자</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3885,76 +3902,56 @@
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>FK/UQ</t>
+          <t>IDX</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>synced_at</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
+          <t>서버 반영 일시. NULL 이면 미전송</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>page_texts</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>raw_text</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>추출 원문</t>
-        </is>
-      </c>
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>[page_texts] 페이지 텍스트 캐시</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr"/>
+      <c r="C95" s="4" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3964,24 +3961,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>norm_text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
+          <t>page_fts 의 content_rowid</t>
         </is>
       </c>
     </row>
@@ -3993,24 +3998,28 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>nospace_text</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>FK/UQ</t>
+        </is>
+      </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -4022,24 +4031,28 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>bigram_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
+          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4064,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>word_boxes</t>
+          <t>raw_text</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4068,7 +4081,7 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>단어 bbox JSON. 선택·하이라이트용</t>
+          <t>추출 원문</t>
         </is>
       </c>
     </row>
@@ -4080,28 +4093,24 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>is_ocr</t>
+          <t>norm_text</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>OCR 로 얻은 텍스트 여부</t>
+          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
         </is>
       </c>
     </row>
@@ -4113,28 +4122,24 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>char_count</t>
+          <t>nospace_text</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>문자 수. 텍스트 레이어 유효성 판정</t>
+          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
         </is>
       </c>
     </row>
@@ -4146,53 +4151,65 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>hangul_ratio</t>
+          <t>bigram_text</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
+          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>[jobs] 서버 작업</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr"/>
-      <c r="C103" s="4" t="inlineStr"/>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>page_texts</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>word_boxes</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>단어 bbox JSON. 선택·하이라이트용</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>is_ocr</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4207,34 +4224,30 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>OCR 로 얻은 텍스트 여부</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4242,32 +4255,32 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>작업 고유 ID</t>
+          <t>문자 수. 텍스트 레이어 유효성 판정</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>hangul_ratio</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4275,46 +4288,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
+          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>jobs</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>대상 책 (신규 생성이면 NULL)</t>
-        </is>
-      </c>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>[jobs] 서버 작업</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr"/>
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4324,24 +4321,32 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>영상 URL 또는 업로드 파일 식별자</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4358,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4366,19 +4371,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>'QUEUED'</t>
-        </is>
-      </c>
+      <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
+          <t>작업 고유 ID</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4391,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>stage_progress</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4403,15 +4404,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>현재 단계 진행률 (0.0~1.0)</t>
+          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4420,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>checkpoint</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4437,10 +4434,14 @@
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
+          <t>대상 책 (신규 생성이면 NULL)</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4453,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4469,7 +4470,7 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>실패 사유. 사용자에게 그대로 노출</t>
+          <t>영상 URL 또는 업로드 파일 식별자</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4482,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>retry_count</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4496,13 +4497,17 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
+          <t>'QUEUED'</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>재시도 횟수</t>
+          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4519,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>stage_progress</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4527,11 +4532,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>현재 단계 진행률 (0.0~1.0)</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4552,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>checkpoint</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4553,39 +4562,55 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>최종 갱신 일시</t>
+          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>[video_books] 영상북 메타 (v2)</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr"/>
-      <c r="C116" s="4" t="inlineStr"/>
-      <c r="D116" s="4" t="inlineStr"/>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>error_message</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>실패 사유. 사용자에게 그대로 노출</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>retry_count</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4598,27 +4623,27 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>PK/FK</t>
-        </is>
-      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>books.id (1:1)</t>
+          <t>재시도 횟수</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4631,27 +4656,23 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>'youtube'</t>
-        </is>
-      </c>
+      <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>출처 (youtube / local)</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>video_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4661,45 +4682,29 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>영상 ID</t>
+          <t>최종 갱신 일시</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>video_books</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>video_url</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
-        </is>
-      </c>
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>[video_books] 영상북 메타 (v2)</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr"/>
+      <c r="C120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4709,24 +4714,28 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>PK/FK</t>
+        </is>
+      </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>채널/업로더</t>
+          <t>books.id (1:1)</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4747,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>duration_sec</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4753,13 +4762,13 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>'youtube'</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>영상 길이(초)</t>
+          <t>출처 (youtube / local)</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4780,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>transcript_source</t>
+          <t>video_id</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4781,14 +4790,14 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
+          <t>영상 ID</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4809,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>sync_path</t>
+          <t>video_url</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4817,7 +4826,7 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>sync.json 경로</t>
+          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4838,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4839,44 +4848,64 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>채널/업로더</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>[video_segments] 영상 세그먼트 (v2)</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr"/>
-      <c r="C126" s="4" t="inlineStr"/>
-      <c r="D126" s="4" t="inlineStr"/>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>video_books</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>duration_sec</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>영상 길이(초)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>transcript_source</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -4884,69 +4913,57 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>sync_path</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
+      <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>sync.json 경로</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>seg_index</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -4958,42 +4975,22 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>세그먼트 순번</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>video_segments</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>t_start</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>REAL</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>시작 시각(초)</t>
-        </is>
-      </c>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>[video_segments] 영상 세그먼트 (v2)</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr"/>
+      <c r="C130" s="4" t="inlineStr"/>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5003,12 +5000,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>t_end</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5016,11 +5013,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>종료 시각(초)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5037,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -5048,12 +5053,12 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>FK/IDX</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>대응 페이지</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -5065,24 +5070,24 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>seg_index</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+          <t>세그먼트 순번</t>
         </is>
       </c>
     </row>
@@ -5094,24 +5099,28 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>t_start</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>해당 구간 텍스트</t>
+          <t>시작 시각(초)</t>
         </is>
       </c>
     </row>
@@ -5123,22 +5132,142 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>chapter_title</t>
+          <t>t_end</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>종료 시각(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>page_no</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>대응 페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>해당 구간 텍스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>chapter_title</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>소속 챕터 제목</t>
         </is>

--- a/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
+++ b/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2289,64 +2289,68 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>book_settings</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>crop_enabled</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>자동 여백 크롭 사용 여부</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>읽기 밝기 배율. 1.0 이 원본</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>book_settings</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>crop_odd</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>홀수 페이지 크롭 [l,t,r,b] 비율 JSON. 제본 여백 때문에 홀짝 분리 계산 필요</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>읽기 대비 배율. 1.0 이 원본. 중간값(128) 기준으로 벌린다</t>
         </is>
       </c>
     </row>
@@ -2358,24 +2362,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>crop_even</t>
+          <t>crop_enabled</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>짝수 페이지 크롭 [l,t,r,b] 비율 JSON</t>
+          <t>자동 여백 크롭 사용 여부</t>
         </is>
       </c>
     </row>
@@ -2387,28 +2395,24 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>column_mode</t>
+          <t>crop_odd</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>다단 순차 보기 컬럼 수 (0=사용안함)</t>
+          <t>홀수 페이지 크롭 [l,t,r,b] 비율 JSON. 제본 여백 때문에 홀짝 분리 계산 필요</t>
         </is>
       </c>
     </row>
@@ -2420,92 +2424,90 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>show_source_annots</t>
+          <t>crop_even</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
+          <t>짝수 페이지 크롭 [l,t,r,b] 비율 JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>column_mode</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>다단 순차 보기 컬럼 수 (0=사용안함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>show_source_annots</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
           <t>원본 PDF 주석 표시 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>book_settings</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>split_pages</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>한 장에 든 두 쪽을 좌·우로 나눠 보기. 펼쳐 스캔한 책은 그대로 보면 글자가 절반 크기가 된다</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>book_settings</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>split_right_to_left</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>분할 시 오른쪽 반쪽을 먼저 읽는가 (세로쓰기 등)</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2519,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>split_prompted</t>
+          <t>split_pages</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2537,7 +2539,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>좌우 분할을 권해 봤는가. 거절한 사람에게 매번 묻지 않기 위함</t>
+          <t>한 장에 든 두 쪽을 좌·우로 나눠 보기. 펼쳐 스캔한 책은 그대로 보면 글자가 절반 크기가 된다</t>
         </is>
       </c>
     </row>
@@ -2549,87 +2551,108 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>split_right_to_left</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>분할 시 오른쪽 반쪽을 먼저 읽는가 (세로쓰기 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>split_prompted</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>좌우 분할을 권해 봤는가. 거절한 사람에게 매번 묻지 않기 위함</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>crop_prompted</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>자동 여백 크롭을 권해 봤는가. 거절한 사람에게 매번 묻지 않기 위함</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>book_settings</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>최종 수정 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>[anchors] 앵커 (주석·캡처 공유)</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>anchors</t>
+          <t>book_settings</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2637,54 +2660,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>최종 수정 일시</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>동기화 기준 전역 고유 ID</t>
-        </is>
-      </c>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>[anchors] 앵커 (주석·캡처 공유)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2694,7 +2689,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2707,15 +2702,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>FK/IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2726,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2740,15 +2739,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>'text'</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2759,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2776,12 +2775,12 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>FK/IDX</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>페이지 번호 (1부터)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2792,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>rects</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2806,11 +2805,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>'text'</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
+          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
         </is>
       </c>
     </row>
@@ -2822,24 +2825,28 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>quote_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
+          <t>페이지 번호 (1부터)</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2858,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>prefix_text</t>
+          <t>rects</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2861,14 +2868,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
+          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2887,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>suffix_text</t>
+          <t>quote_text</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2897,7 +2904,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>뒤 문맥 40자</t>
+          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2916,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>document_checksum</t>
+          <t>prefix_text</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2919,14 +2926,14 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
+          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2945,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>video_time_ms</t>
+          <t>suffix_text</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2955,7 +2962,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
+          <t>뒤 문맥 40자</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2974,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>is_orphan</t>
+          <t>document_checksum</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2980,15 +2987,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
+          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
         </is>
       </c>
     </row>
@@ -3000,54 +3003,74 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>video_time_ms</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>[annotations] 주석</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr"/>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>anchors</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>is_orphan</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3055,54 +3078,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>annotations</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
-        </is>
-      </c>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>[annotations] 주석</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3112,7 +3107,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3125,15 +3120,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>FK/IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3144,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>anchor_id</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3161,12 +3160,12 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>anchors.id</t>
+          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3177,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>anno_type</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3192,10 +3191,14 @@
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>주석 유형 (highlight / underline / strikeout / note)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3210,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>color_slot</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3220,15 +3223,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
+          <t>anchors.id</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3243,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>anno_type</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3250,14 +3253,14 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>사용자 메모</t>
+          <t>주석 유형 (highlight / underline / strikeout / note)</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3272,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>color_slot</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3282,11 +3285,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3305,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3308,14 +3315,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>최종 수정 일시</t>
+          <t>사용자 메모</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3334,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3337,99 +3344,87 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>소프트 삭제</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>[captures] 캡처 기록</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="4" t="inlineStr"/>
-      <c r="D75" s="4" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>annotations</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>최종 수정 일시</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>소프트 삭제</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>captures</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>동기화 기준 전역 고유 ID</t>
-        </is>
-      </c>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>[captures] 캡처 기록</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr"/>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3439,7 +3434,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3452,15 +3447,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>FK/IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3471,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>anchor_id</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3488,12 +3487,12 @@
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3505,24 +3504,28 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>image_path</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>저장된 이미지 경로</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3537,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3547,15 +3550,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>캡처 해상도 (150/300/600)</t>
+          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3570,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ocr_text</t>
+          <t>image_path</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3584,7 +3587,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>영역 OCR 결과 (서버 처리)</t>
+          <t>저장된 이미지 경로</t>
         </is>
       </c>
     </row>
@@ -3596,24 +3599,28 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>캡처 해상도 (150/300/600)</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3632,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>ocr_text</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3635,44 +3642,60 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>영역 OCR 결과 (서버 처리)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>[annotation_events] 주석 이벤트 (append-only)</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="4" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="5" t="inlineStr"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>captures</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3680,54 +3703,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>annotation_events</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>이벤트 고유 ID</t>
-        </is>
-      </c>
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>[annotation_events] 주석 이벤트 (append-only)</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr"/>
+      <c r="C87" s="4" t="inlineStr"/>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3737,12 +3732,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>target_type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3750,11 +3745,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>대상 종류 (annotation / bookmark / capture)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3769,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>target_uuid</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3782,12 +3785,12 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>대상 레코드 UUID</t>
+          <t>이벤트 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3802,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>op</t>
+          <t>target_type</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3816,7 +3819,7 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>연산 (create / update / delete)</t>
+          <t>대상 종류 (annotation / bookmark / capture)</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>target_uuid</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3838,14 +3841,18 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>변경 내용 JSON</t>
+          <t>대상 레코드 UUID</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3864,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>device_id</t>
+          <t>op</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3874,7 +3881,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>작성 기기 식별자</t>
+          <t>연산 (create / update / delete)</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3893,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3896,18 +3903,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+      <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
+          <t>변경 내용 JSON</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3922,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>synced_at</t>
+          <t>device_id</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3929,99 +3932,91 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>서버 반영 일시. NULL 이면 미전송</t>
+          <t>작성 기기 식별자</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>[page_texts] 페이지 텍스트 캐시</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr"/>
-      <c r="C95" s="4" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>annotation_events</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>synced_at</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>page_fts 의 content_rowid</t>
+          <t>서버 반영 일시. NULL 이면 미전송</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>page_texts</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>FK/UQ</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>books.id</t>
-        </is>
-      </c>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>[page_texts] 페이지 텍스트 캐시</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr"/>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4031,7 +4026,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4044,15 +4039,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
+          <t>page_fts 의 content_rowid</t>
         </is>
       </c>
     </row>
@@ -4064,24 +4063,28 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>raw_text</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>FK/UQ</t>
+        </is>
+      </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>추출 원문</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -4093,24 +4096,28 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>norm_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
+          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4129,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>nospace_text</t>
+          <t>raw_text</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4139,7 +4146,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
+          <t>추출 원문</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4158,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>bigram_text</t>
+          <t>norm_text</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4168,7 +4175,7 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
+          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4187,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>word_boxes</t>
+          <t>nospace_text</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4197,7 +4204,7 @@
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>단어 bbox JSON. 선택·하이라이트용</t>
+          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
         </is>
       </c>
     </row>
@@ -4209,28 +4216,24 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>is_ocr</t>
+          <t>bigram_text</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>OCR 로 얻은 텍스트 여부</t>
+          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
         </is>
       </c>
     </row>
@@ -4242,28 +4245,24 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>char_count</t>
+          <t>word_boxes</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>문자 수. 텍스트 레이어 유효성 판정</t>
+          <t>단어 bbox JSON. 선택·하이라이트용</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4274,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>hangul_ratio</t>
+          <t>is_ocr</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4290,43 +4289,63 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
+          <t>OCR 로 얻은 텍스트 여부</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>[jobs] 서버 작업</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr"/>
-      <c r="C107" s="4" t="inlineStr"/>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>page_texts</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>char_count</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>문자 수. 텍스트 레이어 유효성 판정</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>hangul_ratio</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4336,52 +4355,28 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>jobs</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>작업 고유 ID</t>
-        </is>
-      </c>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>[jobs] 서버 작업</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr"/>
+      <c r="C109" s="4" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4391,12 +4386,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4404,11 +4399,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -4420,28 +4423,28 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>대상 책 (신규 생성이면 NULL)</t>
+          <t>작업 고유 ID</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4456,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4463,14 +4466,14 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>영상 URL 또는 업로드 파일 식별자</t>
+          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
         </is>
       </c>
     </row>
@@ -4482,32 +4485,28 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>'QUEUED'</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
+          <t>대상 책 (신규 생성이면 NULL)</t>
         </is>
       </c>
     </row>
@@ -4519,28 +4518,24 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>stage_progress</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>현재 단계 진행률 (0.0~1.0)</t>
+          <t>영상 URL 또는 업로드 파일 식별자</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4547,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>checkpoint</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4562,14 +4557,22 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>'QUEUED'</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
+          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
         </is>
       </c>
     </row>
@@ -4581,24 +4584,28 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>stage_progress</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>실패 사유. 사용자에게 그대로 노출</t>
+          <t>현재 단계 진행률 (0.0~1.0)</t>
         </is>
       </c>
     </row>
@@ -4610,28 +4617,24 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>retry_count</t>
+          <t>checkpoint</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>재시도 횟수</t>
+          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4646,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>error_message</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4653,14 +4656,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>실패 사유. 사용자에게 그대로 노출</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4675,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>retry_count</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4685,41 +4688,61 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>최종 갱신 일시</t>
+          <t>재시도 횟수</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>[video_books] 영상북 메타 (v2)</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr"/>
-      <c r="C120" s="4" t="inlineStr"/>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4728,49 +4751,25 @@
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>PK/FK</t>
-        </is>
-      </c>
+      <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>books.id (1:1)</t>
+          <t>최종 갱신 일시</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>video_books</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>'youtube'</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>출처 (youtube / local)</t>
-        </is>
-      </c>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>[video_books] 영상북 메타 (v2)</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr"/>
+      <c r="C122" s="4" t="inlineStr"/>
+      <c r="D122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4780,24 +4779,28 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>video_id</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>PK/FK</t>
+        </is>
+      </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>영상 ID</t>
+          <t>books.id (1:1)</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4812,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>video_url</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4819,14 +4822,18 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>'youtube'</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
+          <t>출처 (youtube / local)</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4845,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>video_id</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4855,7 +4862,7 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>채널/업로더</t>
+          <t>영상 ID</t>
         </is>
       </c>
     </row>
@@ -4867,28 +4874,24 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>duration_sec</t>
+          <t>video_url</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>영상 길이(초)</t>
+          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4903,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>transcript_source</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4910,14 +4913,14 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
+          <t>채널/업로더</t>
         </is>
       </c>
     </row>
@@ -4929,24 +4932,28 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>sync_path</t>
+          <t>duration_sec</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>sync.json 경로</t>
+          <t>영상 길이(초)</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4965,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>transcript_source</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4975,37 +4982,53 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>[video_segments] 영상 세그먼트 (v2)</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr"/>
-      <c r="C130" s="4" t="inlineStr"/>
-      <c r="D130" s="4" t="inlineStr"/>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>video_books</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>sync_path</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>sync.json 경로</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5013,54 +5036,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>video_segments</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>books.id</t>
-        </is>
-      </c>
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>[video_segments] 영상 세그먼트 (v2)</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr"/>
+      <c r="C132" s="4" t="inlineStr"/>
+      <c r="D132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5070,7 +5065,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>seg_index</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5083,11 +5078,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>세그먼트 순번</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5102,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>t_start</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5115,12 +5118,12 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>FK/IDX</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>시작 시각(초)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5135,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>t_end</t>
+          <t>seg_index</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5149,7 +5152,7 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>종료 시각(초)</t>
+          <t>세그먼트 순번</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5164,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>t_start</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5182,7 +5185,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>대응 페이지</t>
+          <t>시작 시각(초)</t>
         </is>
       </c>
     </row>
@@ -5194,24 +5197,24 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>t_end</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+          <t>종료 시각(초)</t>
         </is>
       </c>
     </row>
@@ -5223,24 +5226,28 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>해당 구간 텍스트</t>
+          <t>대응 페이지</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5259,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>chapter_title</t>
+          <t>rect</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5268,6 +5275,64 @@
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>해당 구간 텍스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>chapter_title</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>소속 챕터 제목</t>
         </is>

--- a/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
+++ b/apps/bookviewer/docs/BookViewer_DB스키마.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2314,7 +2314,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>읽기 밝기 배율. 1.0 이 원본</t>
@@ -2347,7 +2346,6 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>읽기 대비 배율. 1.0 이 원본. 중간값(128) 기준으로 벌린다</t>
@@ -2640,93 +2638,113 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>book_settings</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>최종 수정 일시</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>zoom_locked</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>확대 배율과 좌우 위치 고정. 세로 밀기는 그대로 — 스캔본은 쪽마다 가장자리가 달라 매번 다시 맞추게 된다</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>[anchors] 앵커 (주석·캡처 공유)</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>pan_x</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>고정했을 때의 좌우 위치(화면 픽셀)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>book_settings</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>landscape_hint_shown</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>내부 순번</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>가로로 보라는 안내를 이미 띄웠는가</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>anchors</t>
+          <t>book_settings</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2740,49 +2758,25 @@
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>동기화 기준 전역 고유 ID</t>
+          <t>최종 수정 일시</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>anchors</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>books.id</t>
-        </is>
-      </c>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[anchors] 앵커 (주석·캡처 공유)</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2792,12 +2786,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2807,13 +2801,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>'text'</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2823,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2841,12 +2839,12 @@
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>페이지 번호 (1부터)</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2856,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>rects</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2872,10 +2870,14 @@
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2889,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>quote_text</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2897,14 +2899,18 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>'text'</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
+          <t>앵커 종류 (text 텍스트범위 / area 사각영역 / point 지점)</t>
         </is>
       </c>
     </row>
@@ -2916,24 +2922,28 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>prefix_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
+          <t>페이지 번호 (1부터)</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2955,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>suffix_text</t>
+          <t>rects</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2955,14 +2965,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>뒤 문맥 40자</t>
+          <t>좌표 JSON [[x0,y0,x1,y1],...] PDF 좌표계</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2984,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>document_checksum</t>
+          <t>quote_text</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2984,14 +2994,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
+          <t>선택된 원문. 파일이 바뀌었을 때 재부착 기준</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3013,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>video_time_ms</t>
+          <t>prefix_text</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3020,7 +3030,7 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
+          <t>앞 문맥 40자 (동일 문구가 여러 개일 때 구분)</t>
         </is>
       </c>
     </row>
@@ -3032,28 +3042,24 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>is_orphan</t>
+          <t>suffix_text</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
+          <t>뒤 문맥 40자</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3071,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>document_checksum</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3082,32 +3088,48 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>앵커 생성 당시 books.file_checksum. 불일치 시 재부착 시도</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>[annotations] 주석</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr"/>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>anchors</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>video_time_ms</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>v2 영상북일 때 원본 영상 타임코드(ms)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>is_orphan</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3122,29 +3144,25 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>재부착 실패로 위치를 잃음. 목록 상단에 경고 그룹으로 노출</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>annotations</t>
+          <t>anchors</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3158,49 +3176,25 @@
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>annotations</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>books.id</t>
-        </is>
-      </c>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>[annotations] 주석</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3210,7 +3204,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>anchor_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3223,15 +3217,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>anchors.id</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3241,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>anno_type</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3257,10 +3255,14 @@
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>주석 유형 (highlight / underline / strikeout / note)</t>
+          <t>동기화 기준 전역 고유 ID. Obsidian 딥링크에도 사용</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3274,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>color_slot</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3285,15 +3287,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3305,24 +3307,28 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>사용자 메모</t>
+          <t>anchors.id</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3340,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>anno_type</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3351,7 +3357,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>주석 유형 (highlight / underline / strikeout / note)</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3369,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>color_slot</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3376,11 +3382,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>최종 수정 일시</t>
+          <t>하이라이트 색 슬롯 1~5 (색상값이 아니라 슬롯을 저장해야 테마 변경에 따라감)</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3402,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3409,37 +3419,53 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>소프트 삭제</t>
+          <t>사용자 메모</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>[captures] 캡처 기록</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>annotations</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3447,31 +3473,23 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>최종 수정 일시</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>captures</t>
+          <t>annotations</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3481,53 +3499,29 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>동기화 기준 전역 고유 ID</t>
+          <t>소프트 삭제</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>captures</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>book_id</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>books.id</t>
-        </is>
-      </c>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>[captures] 캡처 기록</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr"/>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3537,7 +3531,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>anchor_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3550,15 +3544,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3568,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>image_path</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3580,14 +3578,18 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>저장된 이미지 경로</t>
+          <t>동기화 기준 전역 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3601,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3612,15 +3614,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>캡처 해상도 (150/300/600)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -3632,24 +3634,28 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ocr_text</t>
+          <t>anchor_id</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>영역 OCR 결과 (서버 처리)</t>
+          <t>anchors.id — **출처를 절대 잃지 않기 위한 핵심 연결**</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3667,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>image_path</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3678,7 +3684,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>저장된 이미지 경로</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3696,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3703,73 +3709,85 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>캡처 해상도 (150/300/600)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>[annotation_events] 주석 이벤트 (append-only)</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr"/>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>captures</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ocr_text</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>영역 OCR 결과 (서버 처리)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>annotation_events</t>
+          <t>captures</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3783,45 +3801,25 @@
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>이벤트 고유 ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>annotation_events</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>target_type</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>대상 종류 (annotation / bookmark / capture)</t>
-        </is>
-      </c>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>[annotation_events] 주석 이벤트 (append-only)</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr"/>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3831,12 +3829,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>target_uuid</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3844,15 +3842,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>대상 레코드 UUID</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3866,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>op</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3878,10 +3880,14 @@
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>연산 (create / update / delete)</t>
+          <t>이벤트 고유 ID</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3899,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>target_type</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3903,14 +3909,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>변경 내용 JSON</t>
+          <t>대상 종류 (annotation / bookmark / capture)</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3928,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>device_id</t>
+          <t>target_uuid</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3936,10 +3942,14 @@
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>작성 기기 식별자</t>
+          <t>대상 레코드 UUID</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3961,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>op</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3965,14 +3975,10 @@
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+      <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
+          <t>연산 (create / update / delete)</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3990,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>synced_at</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4001,37 +4007,53 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>서버 반영 일시. NULL 이면 미전송</t>
+          <t>변경 내용 JSON</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>[page_texts] 페이지 텍스트 캐시</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr"/>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>annotation_events</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>device_id</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>작성 기기 식별자</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4039,87 +4061,59 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>IDX</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>page_fts 의 content_rowid</t>
+          <t>발생 일시. 이 순서대로 재생하면 어느 기기에서든 같은 결과가 된다</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>page_texts</t>
+          <t>annotation_events</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>synced_at</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>FK/UQ</t>
-        </is>
-      </c>
+      <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>서버 반영 일시. NULL 이면 미전송</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>page_texts</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>page_no</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
-        </is>
-      </c>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>[page_texts] 페이지 텍스트 캐시</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr"/>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4129,24 +4123,32 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>raw_text</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>추출 원문</t>
+          <t>page_fts 의 content_rowid</t>
         </is>
       </c>
     </row>
@@ -4158,24 +4160,28 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>norm_text</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>FK/UQ</t>
+        </is>
+      </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -4187,24 +4193,28 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>nospace_text</t>
+          <t>page_no</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
+          <t>페이지 번호. (book_id, page_no) 복합 유니크</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4226,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>bigram_text</t>
+          <t>raw_text</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4233,7 +4243,7 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
+          <t>추출 원문</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4255,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>word_boxes</t>
+          <t>norm_text</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4262,7 +4272,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>단어 bbox JSON. 선택·하이라이트용</t>
+          <t>NFC+NFKC 정규화. NFC 없으면 macOS 유래 자모분리로 검색이 아예 안 됨</t>
         </is>
       </c>
     </row>
@@ -4274,28 +4284,24 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>is_ocr</t>
+          <t>nospace_text</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>OCR 로 얻은 텍스트 여부</t>
+          <t>공백 제거 사본. 한글 PDF 공백 소실 폴백</t>
         </is>
       </c>
     </row>
@@ -4307,28 +4313,24 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>char_count</t>
+          <t>bigram_text</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>문자 수. 텍스트 레이어 유효성 판정</t>
+          <t>**2글자 겹침 분해 텍스트.** 이 필드를 FTS5 에 넣어 한국어 검색을 성립시킨다</t>
         </is>
       </c>
     </row>
@@ -4340,53 +4342,69 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>hangul_ratio</t>
+          <t>word_boxes</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
+          <t>단어 bbox JSON. 선택·하이라이트용</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>[jobs] 서버 작업</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr"/>
-      <c r="C109" s="4" t="inlineStr"/>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="5" t="inlineStr"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>page_texts</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>is_ocr</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>OCR 로 얻은 텍스트 여부</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4401,34 +4419,30 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>문자 수. 텍스트 레이어 유효성 판정</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>page_texts</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>hangul_ratio</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4436,46 +4450,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>작업 고유 ID</t>
+          <t>한글 비율. CID 폰트 깨짐 감지 → OCR 폴백 제안</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>jobs</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>job_type</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
-        </is>
-      </c>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>[jobs] 서버 작업</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr"/>
+      <c r="C112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4485,7 +4483,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4495,18 +4493,22 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>대상 책 (신규 생성이면 NULL)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4520,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4528,14 +4530,18 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>영상 URL 또는 업로드 파일 식별자</t>
+          <t>작업 고유 ID</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4553,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4560,19 +4566,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>'QUEUED'</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
+          <t>작업 종류 (video_book / ocr / table_extract / annot_export)</t>
         </is>
       </c>
     </row>
@@ -4584,28 +4582,28 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>stage_progress</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>현재 단계 진행률 (0.0~1.0)</t>
+          <t>대상 책 (신규 생성이면 NULL)</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4615,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>checkpoint</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4634,7 +4632,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
+          <t>영상 URL 또는 업로드 파일 식별자</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4644,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4656,14 +4654,22 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>'QUEUED'</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>실패 사유. 사용자에게 그대로 노출</t>
+          <t>QUEUED/FETCHING/TRANSCRIBING/SLIDES/OCR/COMPOSING/DONE/FAILED</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4681,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>retry_count</t>
+          <t>stage_progress</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4690,13 +4696,13 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>재시도 횟수</t>
+          <t>현재 단계 진행률 (0.0~1.0)</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4714,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>checkpoint</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4718,14 +4724,14 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>**단계별 산출물 경로 JSON. 중단 시 이 지점부터 재개**</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4743,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>error_message</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4747,44 +4753,64 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>최종 갱신 일시</t>
+          <t>실패 사유. 사용자에게 그대로 노출</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>[video_books] 영상북 메타 (v2)</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr"/>
-      <c r="C122" s="4" t="inlineStr"/>
-      <c r="D122" s="4" t="inlineStr"/>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="5" t="inlineStr"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>retry_count</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>재시도 횟수</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4793,26 +4819,22 @@
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>PK/FK</t>
-        </is>
-      </c>
+      <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>books.id (1:1)</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>video_books</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4825,46 +4847,26 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>'youtube'</t>
-        </is>
-      </c>
+      <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>출처 (youtube / local)</t>
+          <t>최종 갱신 일시</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>video_books</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>video_id</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>영상 ID</t>
-        </is>
-      </c>
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>[video_books] 영상북 메타 (v2)</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr"/>
+      <c r="C125" s="4" t="inlineStr"/>
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4874,24 +4876,28 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>video_url</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>PK/FK</t>
+        </is>
+      </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
+          <t>books.id (1:1)</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4909,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4913,14 +4919,18 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>'youtube'</t>
+        </is>
+      </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>채널/업로더</t>
+          <t>출처 (youtube / local)</t>
         </is>
       </c>
     </row>
@@ -4932,28 +4942,24 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>duration_sec</t>
+          <t>video_id</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>영상 길이(초)</t>
+          <t>영상 ID</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4971,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>transcript_source</t>
+          <t>video_url</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4975,14 +4981,14 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
+          <t>원본 URL. 생성 PDF 에도 항상 포함</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5000,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>sync_path</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5011,7 +5017,7 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>sync.json 경로</t>
+          <t>채널/업로더</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5029,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>duration_sec</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5036,78 +5042,90 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>영상 길이(초)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>[video_segments] 영상 세그먼트 (v2)</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr"/>
-      <c r="C132" s="4" t="inlineStr"/>
-      <c r="D132" s="4" t="inlineStr"/>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>video_books</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>transcript_source</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>자막 출처 (manual_sub / auto_sub / whisper)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sync_path</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>AUTOINCREMENT</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>내부 순번</t>
+          <t>sync.json 경로</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>video_segments</t>
+          <t>video_books</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>book_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5116,45 +5134,25 @@
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>FK/IDX</t>
-        </is>
-      </c>
+      <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>books.id</t>
+          <t>생성 일시</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>video_segments</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>seg_index</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>세그먼트 순번</t>
-        </is>
-      </c>
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>[video_segments] 영상 세그먼트 (v2)</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr"/>
+      <c r="C135" s="4" t="inlineStr"/>
+      <c r="D135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5164,12 +5162,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>t_start</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5177,15 +5175,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>AUTOINCREMENT</t>
+        </is>
+      </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>IDX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>시작 시각(초)</t>
+          <t>내부 순번</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5199,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>t_end</t>
+          <t>book_id</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5211,10 +5213,14 @@
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>FK/IDX</t>
+        </is>
+      </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>종료 시각(초)</t>
+          <t>books.id</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5232,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>page_no</t>
+          <t>seg_index</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5240,14 +5246,10 @@
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+      <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>대응 페이지</t>
+          <t>세그먼트 순번</t>
         </is>
       </c>
     </row>
@@ -5259,24 +5261,28 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>rect</t>
+          <t>t_start</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+          <t>시작 시각(초)</t>
         </is>
       </c>
     </row>
@@ -5288,24 +5294,24 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>t_end</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>해당 구간 텍스트</t>
+          <t>종료 시각(초)</t>
         </is>
       </c>
     </row>
@@ -5317,22 +5323,113 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
+          <t>page_no</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>대응 페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>rect</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>페이지 내 영역 [x0,y0,x1,y1]. 영상 재생 위치에 맞춰 책을 자동 스크롤할 때 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>해당 구간 텍스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>video_segments</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>chapter_title</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>소속 챕터 제목</t>
         </is>
